--- a/microsoft/docs/reports/20261008_microsoft_v0.1_重點.xlsx
+++ b/microsoft/docs/reports/20261008_microsoft_v0.1_重點.xlsx
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
       <c r="C3" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="D3" t="n">
         <v>115.9</v>
@@ -516,12 +516,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.084</v>
+        <v>1.082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.344</v>
+        <v>1.34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HTML 引擎重算（與 Excel 成品 cmp31 543 項一致）；dist/20261009_Microsoft收支模型_v0_1.xlsx「AI增量報酬」頁</t>
+          <t>HTML 引擎重算（與 Excel 成品 cmp31 基準 553 項一致）；dist/20261009_Microsoft收支模型_v0_1.xlsx「AI增量報酬」頁</t>
         </is>
       </c>
     </row>
@@ -739,16 +739,16 @@
         <v>204.2</v>
       </c>
       <c r="C3" t="n">
-        <v>216.1</v>
+        <v>216.2</v>
       </c>
       <c r="D3" t="n">
-        <v>221.9</v>
+        <v>222</v>
       </c>
       <c r="E3" t="n">
-        <v>266.1</v>
+        <v>267.2</v>
       </c>
       <c r="F3" t="n">
-        <v>373.1</v>
+        <v>374.7</v>
       </c>
     </row>
     <row r="4">
@@ -761,16 +761,16 @@
         <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="D4" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="E4" t="n">
-        <v>89.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="F4" t="n">
-        <v>32.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="5">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="n">
         <v>22.3</v>
@@ -792,7 +792,7 @@
         <v>22.3</v>
       </c>
       <c r="F5" t="n">
-        <v>17.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
@@ -805,7 +805,7 @@
         <v>22.3</v>
       </c>
       <c r="C6" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -880,7 +880,7 @@
         <v>0.83</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -893,16 +893,16 @@
         <v>204.2</v>
       </c>
       <c r="C11" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="D11" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="E11" t="n">
-        <v>100.8</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>105.5</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="12">
@@ -915,16 +915,16 @@
         <v>-2.2</v>
       </c>
       <c r="C12" t="n">
-        <v>170.7</v>
+        <v>170.3</v>
       </c>
       <c r="D12" t="n">
-        <v>169.7</v>
+        <v>168.6</v>
       </c>
       <c r="E12" t="n">
-        <v>186.9</v>
+        <v>185.8</v>
       </c>
       <c r="F12" t="n">
-        <v>206.7</v>
+        <v>201.3</v>
       </c>
     </row>
     <row r="13">
@@ -1034,7 +1034,7 @@
         <v>1.01</v>
       </c>
       <c r="F17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="19">
@@ -1044,19 +1044,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>205.9</v>
+        <v>209.7</v>
       </c>
       <c r="C19" t="n">
-        <v>217.8</v>
+        <v>221.7</v>
       </c>
       <c r="D19" t="n">
-        <v>223.6</v>
+        <v>227.4</v>
       </c>
       <c r="E19" t="n">
-        <v>267.8</v>
+        <v>272.6</v>
       </c>
       <c r="F19" t="n">
-        <v>375.9</v>
+        <v>383.5</v>
       </c>
     </row>
     <row r="20">
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.1</v>
+        <v>-4.9</v>
       </c>
       <c r="C20" t="n">
-        <v>40.5</v>
+        <v>36.8</v>
       </c>
       <c r="D20" t="n">
-        <v>84.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>88.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="F20" t="n">
-        <v>30.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="21">
@@ -1100,7 +1100,7 @@
         <v>22.3</v>
       </c>
       <c r="F21" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9.4</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="23">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.7</v>
+        <v>25.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="24">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="C25" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="D25" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="E25" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>三情境目標價（US$／股；現價 529.76、共識 587.63）</t>
+          <t>三情境目標價（US$／股；現價 529.76、共識 587.63；主值待 Andy 決定）</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>讀法 1（主值 D2）</t>
+          <t>讀法 1（D2）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>385.73</v>
+        <v>382.25</v>
       </c>
       <c r="C3" t="n">
-        <v>410.44</v>
+        <v>407.13</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>357.24</v>
+        <v>353.55</v>
       </c>
       <c r="C4" t="n">
-        <v>426.15</v>
+        <v>422.48</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>356.78</v>
+        <v>351.96</v>
       </c>
       <c r="C5" t="n">
-        <v>426.13</v>
+        <v>422.39</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>397.7</v>
+        <v>394.22</v>
       </c>
       <c r="C8" t="n">
-        <v>385.73</v>
+        <v>382.25</v>
       </c>
       <c r="D8" t="n">
-        <v>357.26</v>
+        <v>354.54</v>
       </c>
     </row>
     <row r="9">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>351.48</v>
+        <v>347.84</v>
       </c>
       <c r="C9" t="n">
-        <v>357.24</v>
+        <v>353.55</v>
       </c>
       <c r="D9" t="n">
-        <v>520.6</v>
+        <v>517.88</v>
       </c>
     </row>
     <row r="10">
@@ -1362,36 +1362,207 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>350.74</v>
+        <v>345.48</v>
       </c>
       <c r="C10" t="n">
-        <v>356.78</v>
+        <v>351.96</v>
       </c>
       <c r="D10" t="n">
-        <v>522.64</v>
+        <v>524.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>評價口徑敏感度（基準 $353.55；賣出門檻 $450.30）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>目標價</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>評等</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WACC 9%</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>411.72</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WACC 10%</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WACC 11%</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>351.09</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ERP 4%</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ERP 6%</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>329.63</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>非 AI 改用自身 15.67×</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>414.84</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI 雲端 15×</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>396.58</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>組合：WACC 9%＋自身倍數＋AI 15×</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>519.6900000000001</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>翻轉點</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WACC 8.15%（ERP 2.56%）</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>非 AI 加權倍數 18.05×（基準 11.56×）</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AI 雲端 26.2×</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>終值占比</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>94.5%（&gt; 90%：封鎖買進）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>對外比例 ±20pt（C23）</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>287.99</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C23" t="n">
+        <v>283.83</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>387.51</v>
+      <c r="E23" t="n">
+        <v>383.95</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +2128,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Derived]</t>
+          <t>[Analogy]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1998,7 +2169,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Derived]</t>
+          <t>[Analogy]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2039,7 +2210,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Assumed]</t>
+          <t>[Analogy]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3168,7 +3339,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>−$69.3／+$30.3</t>
+          <t>−$69.7／+$30.4</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3351,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長約 0.76 × 70%＋現貨 1.76 × 30%＝1.06</t>
+          <t>長約 0.76 [Analogy：neocloud 買價代理賣價，偏保守] × 70%＋現貨 1.76 × 30%＝1.06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3212,7 +3383,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+$163.4（上限）</t>
+          <t>+$164.3（上限）</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3405,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>−$5.8</t>
+          <t>−$5.7</t>
         </is>
       </c>
     </row>
@@ -3246,17 +3417,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>→ Hopper × 1.0，新增 MW 的 10%</t>
+          <t>Maia 100 → Hopper、Maia 200 → GB300，× 1.0；新增 MW 的 10%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>× 0.7</t>
+          <t>× 0.7 單邊／雙邊</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>−$1.4</t>
+          <t>−$1.7／+$1.5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3449,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+$6.2／−$17.8</t>
+          <t>+$6.2／−$18.1</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3483,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>自用 50% 全額＋對外 50% 淨額</t>
+          <t>自用 50% 全額＋對外 50% 淨額；5 年合約＋續約 5 年（與 rentedExt 一致）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3322,7 +3493,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>−$11.0／+$10.8</t>
+          <t>−$13.5／+$13.2</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3505,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 ×（曆年 2026 約 175 − FY26 下半年 72.9）＝204.2，含融資租賃</t>
+          <t>204.2（曆年 2026 約 175 換算），含融資租賃</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3344,7 +3515,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>基準速度 2,376 MW-IT／年</t>
+          <t>基準速度 2,325.9 MW-IT／年</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3735,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+$4.6／−$4.4</t>
+          <t>+$4.5／−$4.3</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3801,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>−$13.2／+$4.1</t>
+          <t>−$13.1／+$4.1</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3845,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>+$19.1／+$42.9</t>
+          <t>+$19.1／+$43.0</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3867,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>−$16.7</t>
+          <t>−$17.0</t>
         </is>
       </c>
     </row>
